--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-27).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-27).xlsx
@@ -912,66 +912,69 @@
   </si>
   <si>
     <t>214
-135</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>R$ 1.379.301,21</t>
-  </si>
-  <si>
-    <t>R$ 9.645,46
-R$ 9.788,21</t>
-  </si>
-  <si>
-    <t>(1.7%)
-(0.3%)</t>
-  </si>
-  <si>
-    <t>104.9</t>
-  </si>
-  <si>
-    <t>(5.2%)</t>
-  </si>
-  <si>
-    <t>32.4%</t>
-  </si>
-  <si>
-    <t>(11.0%)</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>61.9%</t>
-  </si>
-  <si>
-    <t>16.0%</t>
-  </si>
-  <si>
-    <t>7.7</t>
-  </si>
-  <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>62.0%</t>
-  </si>
-  <si>
-    <t>-R$ 35.779,09</t>
-  </si>
-  <si>
-    <t>2.95</t>
+167</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 1.672.950,79</t>
+  </si>
+  <si>
+    <t>R$ 9.451,70
+R$ 9.628,16</t>
+  </si>
+  <si>
+    <t>(3.4%)
+(1.9%)</t>
+  </si>
+  <si>
+    <t>102.8</t>
+  </si>
+  <si>
+    <t>(7.0%)</t>
+  </si>
+  <si>
+    <t>33.3%</t>
+  </si>
+  <si>
+    <t>(10.3%)</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>30.7</t>
+  </si>
+  <si>
+    <t>59.7%</t>
+  </si>
+  <si>
+    <t>17.5%</t>
+  </si>
+  <si>
+    <t>7.6</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>22.4</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>-R$ 43.869,46</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1408,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>4.7216663636363636</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>10.75515</v>
+      </c>
       <c r="AD3" s="8">
         <v>17.699393636363634</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.0145161290322582</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>11.145878</v>
+      </c>
       <c r="AD4" s="8">
         <v>16.390322580645162</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>11.294805194805196</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>17.435281</v>
+      </c>
       <c r="AD5" s="8">
         <v>23.092307692307692</v>
       </c>
@@ -2230,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>3.6351015151515149</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>12.894553</v>
+      </c>
       <c r="AD7" s="8">
         <v>19.763183582089553</v>
       </c>
@@ -2361,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>5.5524634782608704</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>29.273582999999999</v>
+      </c>
       <c r="AD8" s="8">
         <v>36.374347826086961</v>
       </c>
@@ -2490,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>4.6949492424242427</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>14.457013</v>
+      </c>
       <c r="AD9" s="8">
         <v>20.49874661654135</v>
       </c>
@@ -2617,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>2.4420095890410956</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>10.634575999999999</v>
+      </c>
       <c r="AD10" s="8">
         <v>17.597260273972601</v>
       </c>
@@ -2668,7 +2685,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>44</v>
@@ -2704,25 +2721,61 @@
       <c t="s" r="N11" s="4">
         <v>52</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="6"/>
+      <c r="O11" s="5">
+        <v>13595.43</v>
+      </c>
+      <c r="P11" s="5">
+        <v>13595.43</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>-0.041501428713438759</v>
+      </c>
+      <c r="R11" s="7">
+        <v>138</v>
+      </c>
+      <c r="S11" s="6">
+        <v>-0.067567567567567544</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0.32387098458820351</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0.026032666859378481</v>
+      </c>
+      <c r="V11" s="6">
+        <v>0.027381039069746229</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.0062379049430580716</v>
+      </c>
+      <c r="X11" s="8">
+        <v>24.164563106796116</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>0.41747572815533979</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0.0097087378640776691</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>5.2731417266187046</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>4.9498346534653459</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>10.495422</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>16.193041747572813</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0.80582524271844658</v>
+      </c>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="5"/>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
       <c r="AH11" s="10">
         <v>3</v>
       </c>
@@ -2841,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>6.298632089552239</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>10.133925</v>
+      </c>
       <c r="AD12" s="8">
         <v>16.839828676470589</v>
       </c>
@@ -2892,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2928,25 +2983,59 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
+      <c r="O13" s="5">
+        <v>17216.869999999999</v>
+      </c>
+      <c r="P13" s="5">
+        <v>17216.869999999999</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.085298404157410745</v>
+      </c>
+      <c r="R13" s="7">
+        <v>181</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.034285714285714253</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.325507243767305</v>
+      </c>
+      <c r="U13" s="6">
+        <v>-0.0091255901914807994</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.018439472447663256</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.013074966588003513</v>
+      </c>
+      <c r="X13" s="8">
+        <v>34.874147244094488</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.3543307086614173</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.31496062992125984</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>7.4502762430939224</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>10.281496062992126</v>
+      </c>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="AD13" s="8">
+        <v>25.27178503937008</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.36220472440944884</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-435.89999999999998</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3065,7 +3154,9 @@
       <c r="AB14" s="8">
         <v>4.6539082758620687</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>13.94957</v>
+      </c>
       <c r="AD14" s="8">
         <v>20.859589041095891</v>
       </c>
@@ -3194,7 +3285,9 @@
       <c r="AB15" s="8">
         <v>3.437593984962406</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>13.118964999999999</v>
+      </c>
       <c r="AD15" s="8">
         <v>19.99666666666667</v>
       </c>
@@ -3323,7 +3416,9 @@
       <c r="AB16" s="8">
         <v>5.5325000000000006</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>12.092817</v>
+      </c>
       <c r="AD16" s="8">
         <v>18.855834999999999</v>
       </c>
@@ -3374,7 +3469,7 @@
         <v>19521</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>44</v>
@@ -3410,10 +3505,16 @@
       <c t="s" r="N17" s="4">
         <v>52</v>
       </c>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="7"/>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
@@ -3428,7 +3529,9 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="6"/>
       <c r="AF17" s="9"/>
-      <c r="AG17" s="5"/>
+      <c r="AG17" s="5">
+        <v>0</v>
+      </c>
       <c r="AH17" s="10">
         <v>5</v>
       </c>
@@ -3547,7 +3650,9 @@
       <c r="AB18" s="8">
         <v>5.3766666666666669</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>10.30236</v>
+      </c>
       <c r="AD18" s="8">
         <v>17.244305833333332</v>
       </c>
@@ -3676,7 +3781,9 @@
       <c r="AB19" s="8">
         <v>5.1625736842105265</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>7.3473179999999996</v>
+      </c>
       <c r="AD19" s="8">
         <v>13.983333898305085</v>
       </c>
@@ -3805,7 +3912,9 @@
       <c r="AB20" s="8">
         <v>5.1210253846153844</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>20.060165999999999</v>
+      </c>
       <c r="AD20" s="8">
         <v>26.975063358778623</v>
       </c>
@@ -3934,7 +4043,9 @@
       <c r="AB21" s="8">
         <v>5.3871106666666666</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>9.6875549999999997</v>
+      </c>
       <c r="AD21" s="8">
         <v>15.639110666666665</v>
       </c>
@@ -4063,7 +4174,9 @@
       <c r="AB22" s="8">
         <v>5.5232029411764714</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>12.614946</v>
+      </c>
       <c r="AD22" s="8">
         <v>19.284920952380951</v>
       </c>
@@ -4192,7 +4305,9 @@
       <c r="AB23" s="8">
         <v>5.0690999999999997</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>13.931718999999999</v>
+      </c>
       <c r="AD23" s="8">
         <v>20.396064583333334</v>
       </c>
@@ -4416,7 +4531,9 @@
       <c r="AB25" s="8">
         <v>20.327545833333332</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>30.318722000000001</v>
+      </c>
       <c r="AD25" s="8">
         <v>31.892744705882354</v>
       </c>
@@ -4467,7 +4584,7 @@
         <v>19540</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C26" s="4">
         <v>44</v>
@@ -4503,25 +4620,61 @@
       <c t="s" r="N26" s="4">
         <v>52</v>
       </c>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="6"/>
+      <c r="O26" s="5">
+        <v>14067.030000000001</v>
+      </c>
+      <c r="P26" s="5">
+        <v>14067.030000000001</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>-0.20185614717543809</v>
+      </c>
+      <c r="R26" s="7">
+        <v>143</v>
+      </c>
+      <c r="S26" s="6">
+        <v>-0.18285714285714283</v>
+      </c>
+      <c r="T26" s="6">
+        <v>0.34187275494542912</v>
+      </c>
+      <c r="U26" s="6">
+        <v>0.016466468046204493</v>
+      </c>
+      <c r="V26" s="6">
+        <v>0.027174392888904053</v>
+      </c>
+      <c r="W26" s="6">
+        <v>0.0086516485711624989</v>
+      </c>
+      <c r="X26" s="8">
+        <v>26.150495049504947</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>0.68316831683168322</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>0.039603960396039604</v>
+      </c>
+      <c r="AA26" s="8">
+        <v>2.8036613636363636</v>
+      </c>
+      <c r="AB26" s="8">
+        <v>9.6788197916666672</v>
+      </c>
+      <c r="AC26" s="8">
+        <v>12.479162000000001</v>
+      </c>
+      <c r="AD26" s="8">
+        <v>18.571121782178217</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>0.68316831683168322</v>
+      </c>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="5"/>
+      <c r="AG26" s="5">
+        <v>-289.80000000000001</v>
+      </c>
       <c r="AH26" s="10">
         <v>3</v>
       </c>
@@ -4562,7 +4715,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4598,25 +4751,61 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="O27" s="5">
+        <v>6869.5500000000002</v>
+      </c>
+      <c r="P27" s="5">
+        <v>6869.5500000000002</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.4668452244208644</v>
+      </c>
+      <c r="R27" s="7">
+        <v>71</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="T27" s="6">
+        <v>1.7757572766775114</v>
+      </c>
+      <c r="U27" s="6">
+        <v>1.4675449483590628</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.066674673013516164</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.055842813575852857</v>
+      </c>
+      <c r="X27" s="8">
+        <v>27.906504878048779</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.56097560975609762</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.14634146341463414</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>4.8387323943661977</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>7.9700000000000006</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>13.457698000000001</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>21.140243902439025</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.65853658536585369</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>-10.9</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4657,7 +4846,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4693,25 +4882,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>8211.7700000000004</v>
+      </c>
+      <c r="P28" s="5">
+        <v>8211.7700000000004</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.2230634038813839</v>
+      </c>
+      <c r="R28" s="7">
+        <v>89</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.085365853658536661</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00033471468392319803</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.3204012533229742</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.064921752557609375</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.057277846310844066</v>
+      </c>
+      <c r="X28" s="8">
+        <v>24.557576363636365</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.448467816091954</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>7.9930309090909084</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>10.536060000000001</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>17.478787272727274</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.78181818181818186</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1267.6400000000001</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -4830,7 +5055,9 @@
       <c r="AB29" s="8">
         <v>12.518421052631577</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>35.925764999999998</v>
+      </c>
       <c r="AD29" s="8">
         <v>43.233615254237286</v>
       </c>
@@ -4955,7 +5182,9 @@
       <c r="AB30" s="8">
         <v>16.699304166666668</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>20.938638000000001</v>
+      </c>
       <c r="AD30" s="8">
         <v>27.02</v>
       </c>
@@ -5086,7 +5315,9 @@
       <c r="AB31" s="8">
         <v>5.919014084507042</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>15.808427999999999</v>
+      </c>
       <c r="AD31" s="8">
         <v>23.591434722222221</v>
       </c>
@@ -5215,7 +5446,9 @@
       <c r="AB32" s="8">
         <v>4.3121556390977442</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>7.0208009999999996</v>
+      </c>
       <c r="AD32" s="8">
         <v>12.985338345864662</v>
       </c>
@@ -5266,7 +5499,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5300,25 +5533,61 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="O33" s="5">
+        <v>11712.450000000001</v>
+      </c>
+      <c r="P33" s="5">
+        <v>11712.450000000001</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>-0.21908201657386728</v>
+      </c>
+      <c r="R33" s="7">
+        <v>115</v>
+      </c>
+      <c r="S33" s="6">
+        <v>-0.22297297297297303</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.36780168965502519</v>
+      </c>
+      <c r="U33" s="6">
+        <v>0.029285836865899105</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.025679383903453163</v>
+      </c>
+      <c r="W33" s="6">
+        <v>0.0071819730287002283</v>
+      </c>
+      <c r="X33" s="8">
+        <v>27.184392063492066</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.58730158730158732</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>3.261304347826087</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>9.1696241935483869</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>12.520944999999999</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>19.255820634920635</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>0.74603174603174605</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5437,7 +5706,9 @@
       <c r="AB34" s="8">
         <v>3.7271223602484471</v>
       </c>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="8">
+        <v>17.007183000000001</v>
+      </c>
       <c r="AD34" s="8">
         <v>22.857157668711658</v>
       </c>
@@ -5568,7 +5839,9 @@
       <c r="AB35" s="8">
         <v>3.102380952380952</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>13.238853000000001</v>
+      </c>
       <c r="AD35" s="8">
         <v>19.68768115942029</v>
       </c>
@@ -5794,7 +6067,9 @@
       <c r="AB37" s="8">
         <v>22.152810843373494</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>34.668377999999997</v>
+      </c>
       <c r="AD37" s="8">
         <v>40.051326136363635</v>
       </c>
@@ -5923,7 +6198,9 @@
       <c r="AB38" s="8">
         <v>11.300000000000001</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>16.529648999999999</v>
+      </c>
       <c r="AD38" s="8">
         <v>24.30263157894737</v>
       </c>
@@ -5974,7 +6251,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6010,25 +6287,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>16411.080000000002</v>
+      </c>
+      <c r="P39" s="5">
+        <v>16411.080000000002</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.20752901079640917</v>
+      </c>
+      <c r="R39" s="7">
+        <v>179</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.10493827160493829</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.29596915620422298</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.021387775819751046</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.037091160362389311</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.01601942102530729</v>
+      </c>
+      <c r="X39" s="8">
+        <v>35.684244531250002</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.36434108527131781</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.421875</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>4.543223626373627</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>13.90940170940171</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>18.339762</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>24.586328125000001</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.234375</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6147,7 +6460,9 @@
       <c r="AB40" s="8">
         <v>6.4319130681818173</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>11.263059</v>
+      </c>
       <c r="AD40" s="8">
         <v>17.955400558659218</v>
       </c>
@@ -6276,7 +6591,9 @@
       <c r="AB41" s="8">
         <v>12.171808510638298</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>16.661217000000001</v>
+      </c>
       <c r="AD41" s="8">
         <v>22.267708333333331</v>
       </c>
@@ -6422,7 +6739,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6458,25 +6775,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>11930.93</v>
+      </c>
+      <c r="P43" s="5">
+        <v>11930.93</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>-0.057485729092112803</v>
+      </c>
+      <c r="R43" s="7">
+        <v>118</v>
+      </c>
+      <c r="S43" s="6">
+        <v>-0.12592592592592589</v>
+      </c>
+      <c r="T43" s="6">
+        <v>0.33171886852072718</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.0020572914265694292</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.065776976312827237</v>
+      </c>
+      <c r="W43" s="6">
+        <v>0.052608681804352214</v>
+      </c>
+      <c r="X43" s="8">
+        <v>34.100794047619047</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.13095238095238096</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>7.7787353448275862</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>9.3375531645569616</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>17.457706999999999</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>23.610714285714284</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.40476190476190477</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -6595,7 +6948,9 @@
       <c r="AB44" s="8">
         <v>2.5833329545454546</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>7.2235810000000003</v>
+      </c>
       <c r="AD44" s="8">
         <v>14.876949999999999</v>
       </c>
@@ -6724,7 +7079,9 @@
       <c r="AB45" s="8">
         <v>4.7292352459016387</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>11.209208</v>
+      </c>
       <c r="AD45" s="8">
         <v>17.580217073170733</v>
       </c>
@@ -6849,7 +7206,9 @@
       <c r="AB46" s="8">
         <v>7.1063224137931034</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>11.608862999999999</v>
+      </c>
       <c r="AD46" s="8">
         <v>18.25903898305085</v>
       </c>
@@ -6978,7 +7337,9 @@
       <c r="AB47" s="8">
         <v>13.392792792792791</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>21.868603</v>
+      </c>
       <c r="AD47" s="8">
         <v>28.468289380530976</v>
       </c>
@@ -7105,7 +7466,9 @@
       <c r="AB48" s="8">
         <v>4.3231481481481477</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>21.567492999999999</v>
+      </c>
       <c r="AD48" s="8">
         <v>28.313094642857145</v>
       </c>
@@ -7232,7 +7595,9 @@
       <c r="AB49" s="8">
         <v>13.299312371134022</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>19.141064</v>
+      </c>
       <c r="AD49" s="8">
         <v>27.069415463917526</v>
       </c>
@@ -7283,7 +7648,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7319,25 +7684,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>14984</v>
+      </c>
+      <c r="P50" s="5">
+        <v>14984</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.054189082650517695</v>
+      </c>
+      <c r="R50" s="7">
+        <v>172</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.080213903743315496</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.24558304191137212</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.061339008275493857</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.031673651895355044</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.012685397757608116</v>
+      </c>
+      <c r="X50" s="8">
+        <v>25.150317142857144</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.92380952380952386</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0.0095238095238095247</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>3.3357701754385967</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>8.7298409523809521</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>12.050281</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>19.948730476190477</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.73333333333333328</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7551,7 +7952,9 @@
       <c r="AB52" s="8">
         <v>10.80218524590164</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>23.658137</v>
+      </c>
       <c r="AD52" s="8">
         <v>30.193960869565217</v>
       </c>
@@ -7678,7 +8081,9 @@
       <c r="AB53" s="8">
         <v>8.1454728395061728</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>17.695473</v>
+      </c>
       <c r="AD53" s="8">
         <v>24.57469135802469</v>
       </c>
@@ -7729,7 +8134,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>44</v>
@@ -7765,25 +8170,61 @@
       <c t="s" r="N54" s="4">
         <v>52</v>
       </c>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="8"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="8"/>
-      <c r="AB54" s="8"/>
-      <c r="AC54" s="8"/>
-      <c r="AD54" s="8"/>
-      <c r="AE54" s="6"/>
+      <c r="O54" s="5">
+        <v>7974.0600000000004</v>
+      </c>
+      <c r="P54" s="5">
+        <v>7974.0600000000004</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>-0.017531279454434556</v>
+      </c>
+      <c r="R54" s="7">
+        <v>86</v>
+      </c>
+      <c r="S54" s="6">
+        <v>-0.15686274509803921</v>
+      </c>
+      <c r="T54" s="6">
+        <v>1.7697562220499969</v>
+      </c>
+      <c r="U54" s="6">
+        <v>1.4116187111709717</v>
+      </c>
+      <c r="V54" s="6">
+        <v>0.012957389334918471</v>
+      </c>
+      <c r="W54" s="6">
+        <v>-0.0058197455248643719</v>
+      </c>
+      <c r="X54" s="8">
+        <v>29.851436206896551</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0.44827586206896552</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>0.086206896551724144</v>
+      </c>
+      <c r="AA54" s="8">
+        <v>6.94902</v>
+      </c>
+      <c r="AB54" s="8">
+        <v>7.5508620689655173</v>
+      </c>
+      <c r="AC54" s="8">
+        <v>14.521551000000001</v>
+      </c>
+      <c r="AD54" s="8">
+        <v>21.449425862068967</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>0.53448275862068961</v>
+      </c>
       <c r="AF54" s="9"/>
-      <c r="AG54" s="5"/>
+      <c r="AG54" s="5">
+        <v>-522.10000000000002</v>
+      </c>
       <c r="AH54" s="10">
         <v>2</v>
       </c>
@@ -7824,7 +8265,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7860,25 +8301,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>7889.4399999999996</v>
+      </c>
+      <c r="P55" s="5">
+        <v>7889.4399999999996</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.18190820752594172</v>
+      </c>
+      <c r="R55" s="7">
+        <v>99</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.048076923076923128</v>
+      </c>
+      <c r="T55" s="6">
+        <v>1.140765377517289E-05</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.3239824372832546</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.080057710052931524</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.041169018333367134</v>
+      </c>
+      <c r="X55" s="8">
+        <v>52.151741791044778</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.68656716417910446</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>8.6496702970297026</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>24.322980303030306</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>33.075645000000002</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>39.52014925373134</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.089552238805970144</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -7995,7 +8472,9 @@
       <c r="AB56" s="8">
         <v>2.9490275000000001</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>11.287606</v>
+      </c>
       <c r="AD56" s="8">
         <v>19.648497540983605</v>
       </c>
@@ -8124,7 +8603,9 @@
       <c r="AB57" s="8">
         <v>15.82140775862069</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>43.151435999999997</v>
+      </c>
       <c r="AD57" s="8">
         <v>50.064942241379313</v>
       </c>
@@ -8348,7 +8829,9 @@
       <c r="AB59" s="8">
         <v>6.4304687500000002</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>12.659323000000001</v>
+      </c>
       <c r="AD59" s="8">
         <v>19.453333846153846</v>
       </c>
@@ -8399,7 +8882,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>44</v>
@@ -8435,25 +8918,61 @@
       <c t="s" r="N60" s="4">
         <v>52</v>
       </c>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="7"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
-      <c r="X60" s="8"/>
-      <c r="Y60" s="6"/>
-      <c r="Z60" s="6"/>
-      <c r="AA60" s="8"/>
-      <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
-      <c r="AD60" s="8"/>
-      <c r="AE60" s="6"/>
+      <c r="O60" s="5">
+        <v>7797.1499999999996</v>
+      </c>
+      <c r="P60" s="5">
+        <v>7797.1499999999996</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>-0.025934601330460105</v>
+      </c>
+      <c r="R60" s="7">
+        <v>92</v>
+      </c>
+      <c r="S60" s="6">
+        <v>-0.04166666666666663</v>
+      </c>
+      <c r="T60" s="6">
+        <v>0.30556036500516215</v>
+      </c>
+      <c r="U60" s="6">
+        <v>-0.0053237400845180614</v>
+      </c>
+      <c r="V60" s="6">
+        <v>0.02065831746214963</v>
+      </c>
+      <c r="W60" s="6">
+        <v>0.0023221305220497237</v>
+      </c>
+      <c r="X60" s="8">
+        <v>24.232727272727271</v>
+      </c>
+      <c r="Y60" s="6">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="Z60" s="6">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="AA60" s="8">
+        <v>5.3207411111111105</v>
+      </c>
+      <c r="AB60" s="8">
+        <v>3.7225314814814814</v>
+      </c>
+      <c r="AC60" s="8">
+        <v>8.8801050000000004</v>
+      </c>
+      <c r="AD60" s="8">
+        <v>16.621212727272727</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>0.78181818181818186</v>
+      </c>
       <c r="AF60" s="9"/>
-      <c r="AG60" s="5"/>
+      <c r="AG60" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH60" s="10">
         <v>4</v>
       </c>
@@ -8494,7 +9013,7 @@
         <v>19624</v>
       </c>
       <c r="B61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C61" s="4">
         <v>44</v>
@@ -8528,25 +9047,61 @@
       <c t="s" r="N61" s="4">
         <v>52</v>
       </c>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="7"/>
-      <c r="S61" s="6"/>
-      <c r="T61" s="6"/>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="8"/>
-      <c r="Y61" s="6"/>
-      <c r="Z61" s="6"/>
-      <c r="AA61" s="8"/>
-      <c r="AB61" s="8"/>
-      <c r="AC61" s="8"/>
-      <c r="AD61" s="8"/>
-      <c r="AE61" s="6"/>
+      <c r="O61" s="5">
+        <v>9418.6399999999994</v>
+      </c>
+      <c r="P61" s="5">
+        <v>9418.6399999999994</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>0.29427413991172369</v>
+      </c>
+      <c r="R61" s="7">
+        <v>112</v>
+      </c>
+      <c r="S61" s="6">
+        <v>0.21739130434782616</v>
+      </c>
+      <c r="T61" s="6">
+        <v>0.19129091885877367</v>
+      </c>
+      <c r="U61" s="6">
+        <v>-0.15328536816355653</v>
+      </c>
+      <c r="V61" s="6">
+        <v>0.023603885486652001</v>
+      </c>
+      <c r="W61" s="6">
+        <v>0.0015911532875234641</v>
+      </c>
+      <c r="X61" s="8">
+        <v>26.277891836734696</v>
+      </c>
+      <c r="Y61" s="6">
+        <v>0.68000000000000005</v>
+      </c>
+      <c r="Z61" s="6">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="AA61" s="8">
+        <v>1.7236607142857143</v>
+      </c>
+      <c r="AB61" s="8">
+        <v>7.2055562499999999</v>
+      </c>
+      <c r="AC61" s="8">
+        <v>9.0833320000000004</v>
+      </c>
+      <c r="AD61" s="8">
+        <v>15.80578163265306</v>
+      </c>
+      <c r="AE61" s="6">
+        <v>0.81632653061224492</v>
+      </c>
       <c r="AF61" s="9"/>
-      <c r="AG61" s="5"/>
+      <c r="AG61" s="5">
+        <v>-511.30000000000001</v>
+      </c>
       <c r="AH61" s="10">
         <v>3</v>
       </c>
@@ -8663,7 +9218,9 @@
       <c r="AB62" s="8">
         <v>5.1088740259740266</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>9.5082559999999994</v>
+      </c>
       <c r="AD62" s="8">
         <v>16.127291249999999</v>
       </c>
@@ -8714,7 +9271,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -8750,11 +9307,21 @@
       <c t="s" r="N63" s="4">
         <v>52</v>
       </c>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="6"/>
+      <c r="O63" s="5">
+        <v>0</v>
+      </c>
+      <c r="P63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="6">
+        <v>-1</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
@@ -8768,7 +9335,9 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="6"/>
       <c r="AF63" s="9"/>
-      <c r="AG63" s="5"/>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
       <c r="AH63" s="10">
         <v>3</v>
       </c>
@@ -8885,7 +9454,9 @@
       <c r="AB64" s="8">
         <v>10.470334000000001</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>15.227740000000001</v>
+      </c>
       <c r="AD64" s="8">
         <v>21.382703773584907</v>
       </c>
@@ -9107,7 +9678,9 @@
       <c r="AB66" s="8">
         <v>3.1047984848484846</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>12.114746999999999</v>
+      </c>
       <c r="AD66" s="8">
         <v>19.124495454545453</v>
       </c>
@@ -9234,7 +9807,9 @@
       <c r="AB67" s="8">
         <v>13.033085074626864</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>20.092237999999998</v>
+      </c>
       <c r="AD67" s="8">
         <v>26.389285714285716</v>
       </c>
@@ -9363,7 +9938,9 @@
       <c r="AB68" s="8">
         <v>3.5593220338983049</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>9.6262609999999995</v>
+      </c>
       <c r="AD68" s="8">
         <v>16.475140677966102</v>
       </c>
@@ -9490,7 +10067,9 @@
       <c r="AB69" s="8">
         <v>21.859038983050848</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="8">
+        <v>45.407997000000002</v>
+      </c>
       <c r="AD69" s="8">
         <v>51.520903389830508</v>
       </c>
@@ -9619,7 +10198,9 @@
       <c r="AB70" s="8">
         <v>8.8304687499999996</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8">
+        <v>35.323175999999997</v>
+      </c>
       <c r="AD70" s="8">
         <v>42.272656249999997</v>
       </c>
@@ -9670,7 +10251,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9704,25 +10285,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>12629.17</v>
+      </c>
+      <c r="P71" s="5">
+        <v>12629.17</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.20550970876840247</v>
+      </c>
+      <c r="R71" s="7">
+        <v>150</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.21465968586387429</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.26771795771218537</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.045959029769969045</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.024245655098474404</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.0064479692648052095</v>
+      </c>
+      <c r="X71" s="8">
+        <v>41.153846153846153</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.94871794871794868</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.44871794871794873</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>10.787126206896552</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>15.203880821917808</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>27.572631000000001</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>34.100426923076917</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-370.10000000000002</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -9839,7 +10456,9 @@
       <c r="AB72" s="8">
         <v>6.134004697986577</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>12.066789</v>
+      </c>
       <c r="AD72" s="8">
         <v>18.972444666666668</v>
       </c>
@@ -9966,7 +10585,9 @@
       <c r="AB73" s="8">
         <v>10.436428571428571</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>17.438808000000002</v>
+      </c>
       <c r="AD73" s="8">
         <v>25.366904285714284</v>
       </c>
@@ -10108,7 +10729,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10144,25 +10765,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>7000.5900000000001</v>
+      </c>
+      <c r="P75" s="5">
+        <v>7000.5900000000001</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.032345948635722821</v>
+      </c>
+      <c r="R75" s="7">
+        <v>80</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.069767441860465129</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32387984441311374</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.044961710370125953</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.027444615382417766</v>
+      </c>
+      <c r="X75" s="8">
+        <v>23.288235294117644</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.8222972972972977</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>7.0024500000000005</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>12.139704</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>19.089214705882355</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.91176470588235292</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-789</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10203,7 +10860,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10237,25 +10894,59 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
+      <c r="O76" s="5">
+        <v>9678.9500000000007</v>
+      </c>
+      <c r="P76" s="5">
+        <v>9678.9500000000007</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.24300584309594142</v>
+      </c>
+      <c r="R76" s="7">
+        <v>111</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.33532934131736525</v>
+      </c>
+      <c r="T76" s="6">
+        <v>-1.0598612246163066</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-1.4253895102257992</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.01038196291953156</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.0059286906121015183</v>
+      </c>
+      <c r="X76" s="8">
+        <v>29.015422388059701</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.29850746268656714</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>9.3955031746031743</v>
+      </c>
       <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="AD76" s="8">
+        <v>20.515422388059701</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.64179104477611937</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-314.30000000000001</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -10374,7 +11065,9 @@
       <c r="AB77" s="8">
         <v>3.053934722222222</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>7.7324070000000003</v>
+      </c>
       <c r="AD77" s="8">
         <v>14.669906944444445</v>
       </c>
@@ -10499,7 +11192,9 @@
       <c r="AB78" s="8">
         <v>2.7590034482758621</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>8.4508539999999996</v>
+      </c>
       <c r="AD78" s="8">
         <v>16.146296666666668</v>
       </c>
@@ -10550,7 +11245,7 @@
         <v>19671</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>44</v>
@@ -10586,25 +11281,61 @@
       <c t="s" r="N79" s="4">
         <v>52</v>
       </c>
-      <c r="O79" s="5"/>
-      <c r="P79" s="5"/>
-      <c r="Q79" s="6"/>
-      <c r="R79" s="7"/>
-      <c r="S79" s="6"/>
-      <c r="T79" s="6"/>
-      <c r="U79" s="6"/>
-      <c r="V79" s="6"/>
-      <c r="W79" s="6"/>
-      <c r="X79" s="8"/>
-      <c r="Y79" s="6"/>
-      <c r="Z79" s="6"/>
-      <c r="AA79" s="8"/>
-      <c r="AB79" s="8"/>
-      <c r="AC79" s="8"/>
-      <c r="AD79" s="8"/>
-      <c r="AE79" s="6"/>
+      <c r="O79" s="5">
+        <v>9858.0300000000007</v>
+      </c>
+      <c r="P79" s="5">
+        <v>9858.0300000000007</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>-0.090478562927288286</v>
+      </c>
+      <c r="R79" s="7">
+        <v>111</v>
+      </c>
+      <c r="S79" s="6">
+        <v>-0.13953488372093026</v>
+      </c>
+      <c r="T79" s="6">
+        <v>0.33296809808856331</v>
+      </c>
+      <c r="U79" s="6">
+        <v>-0.01194462788204134</v>
+      </c>
+      <c r="V79" s="6">
+        <v>0.021844273145851655</v>
+      </c>
+      <c r="W79" s="6">
+        <v>0.013233019173201948</v>
+      </c>
+      <c r="X79" s="8">
+        <v>34.739166666666662</v>
+      </c>
+      <c r="Y79" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z79" s="6">
+        <v>0.28333333333333333</v>
+      </c>
+      <c r="AA79" s="8">
+        <v>8.0938441441441444</v>
+      </c>
+      <c r="AB79" s="8">
+        <v>14.139655172413793</v>
+      </c>
+      <c r="AC79" s="8">
+        <v>22.994845999999999</v>
+      </c>
+      <c r="AD79" s="8">
+        <v>29.423333333333336</v>
+      </c>
+      <c r="AE79" s="6">
+        <v>0.36666666666666664</v>
+      </c>
       <c r="AF79" s="9"/>
-      <c r="AG79" s="5"/>
+      <c r="AG79" s="5">
+        <v>-496.5</v>
+      </c>
       <c r="AH79" s="10">
         <v>3</v>
       </c>
@@ -10721,7 +11452,9 @@
       <c r="AB80" s="8">
         <v>2.5344704545454544</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>6.166544</v>
+      </c>
       <c r="AD80" s="8">
         <v>15.296541509433961</v>
       </c>
@@ -10852,7 +11585,9 @@
       <c r="AB81" s="8">
         <v>6.6433333333333335</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>11.792776999999999</v>
+      </c>
       <c r="AD81" s="8">
         <v>18.73</v>
       </c>
@@ -10903,7 +11638,7 @@
         <v>19679</v>
       </c>
       <c r="B82" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C82" s="4">
         <v>44</v>
@@ -10939,11 +11674,21 @@
       <c t="s" r="N82" s="4">
         <v>52</v>
       </c>
-      <c r="O82" s="5"/>
-      <c r="P82" s="5"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="7"/>
-      <c r="S82" s="6"/>
+      <c r="O82" s="5">
+        <v>0</v>
+      </c>
+      <c r="P82" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R82" s="7">
+        <v>0</v>
+      </c>
+      <c r="S82" s="6">
+        <v>-1</v>
+      </c>
       <c r="T82" s="6"/>
       <c r="U82" s="6"/>
       <c r="V82" s="6"/>
@@ -10957,7 +11702,9 @@
       <c r="AD82" s="8"/>
       <c r="AE82" s="6"/>
       <c r="AF82" s="9"/>
-      <c r="AG82" s="5"/>
+      <c r="AG82" s="5">
+        <v>0</v>
+      </c>
       <c r="AH82" s="10">
         <v>2</v>
       </c>
@@ -11169,7 +11916,9 @@
       <c r="AB84" s="8">
         <v>7.9352720930232561</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>14.807862999999999</v>
+      </c>
       <c r="AD84" s="8">
         <v>21.264073333333332</v>
       </c>
@@ -11298,7 +12047,9 @@
       <c r="AB85" s="8">
         <v>8.5388916666666663</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>13.415811</v>
+      </c>
       <c r="AD85" s="8">
         <v>14.871052631578948</v>
       </c>
@@ -11427,7 +12178,9 @@
       <c r="AB86" s="8">
         <v>2.1204174999999998</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>9.7208319999999997</v>
+      </c>
       <c r="AD86" s="8">
         <v>18.179167499999998</v>
       </c>
@@ -11556,7 +12309,9 @@
       <c r="AB87" s="8">
         <v>17.822580645161292</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>21.866001000000001</v>
+      </c>
       <c r="AD87" s="8">
         <v>25.940741666666668</v>
       </c>
@@ -11683,7 +12438,9 @@
       <c r="AB88" s="8">
         <v>7.6509999999999998</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>11.294954000000001</v>
+      </c>
       <c r="AD88" s="8">
         <v>17.456435643564355</v>
       </c>
@@ -11695,7 +12452,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -11905,7 +12662,9 @@
       <c r="AB90" s="8">
         <v>21.335135135135136</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>34.586433</v>
+      </c>
       <c r="AD90" s="8">
         <v>40.934210526315788</v>
       </c>
@@ -12034,7 +12793,9 @@
       <c r="AB91" s="8">
         <v>4.0135651162790698</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>12.558244999999999</v>
+      </c>
       <c r="AD91" s="8">
         <v>18.86453829787234</v>
       </c>
@@ -12163,7 +12924,9 @@
       <c r="AB92" s="8">
         <v>6.9825195121951218</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>15.309264000000001</v>
+      </c>
       <c r="AD92" s="8">
         <v>22.679458139534884</v>
       </c>
@@ -12290,7 +13053,9 @@
       <c r="AB93" s="8">
         <v>3.0290557522123893</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>6.0221229999999997</v>
+      </c>
       <c r="AD93" s="8">
         <v>12.963126548672566</v>
       </c>
@@ -12417,7 +13182,9 @@
       <c r="AB94" s="8">
         <v>3.9562499999999998</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>10.736488</v>
+      </c>
       <c r="AD94" s="8">
         <v>18.07619</v>
       </c>
@@ -12639,7 +13406,9 @@
       <c r="AB96" s="8">
         <v>2.7628200000000001</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>5.446402</v>
+      </c>
       <c r="AD96" s="8">
         <v>12.370256923076923</v>
       </c>
@@ -12768,7 +13537,9 @@
       <c r="AB97" s="8">
         <v>1.4995361111111112</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>16.200413999999999</v>
+      </c>
       <c r="AD97" s="8">
         <v>22.166216216216217</v>
       </c>
@@ -12897,7 +13668,9 @@
       <c r="AB98" s="8">
         <v>9.9499999999999993</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>18.084648999999999</v>
+      </c>
       <c r="AD98" s="8">
         <v>24.275439473684209</v>
       </c>
@@ -13026,7 +13799,9 @@
       <c r="AB99" s="8">
         <v>5.8526147058823526</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>11.78805</v>
+      </c>
       <c r="AD99" s="8">
         <v>18.652750485436894</v>
       </c>
@@ -13155,7 +13930,9 @@
       <c r="AB100" s="8">
         <v>5.1000000000000005</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>14.023076</v>
+      </c>
       <c r="AD100" s="8">
         <v>22.815384615384612</v>
       </c>
@@ -13282,7 +14059,9 @@
       <c r="AB101" s="8">
         <v>10.399536111111111</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>15.24208</v>
+      </c>
       <c r="AD101" s="8">
         <v>21.360526315789475</v>
       </c>
@@ -13506,7 +14285,9 @@
       <c r="AB103" s="8">
         <v>4.1031914893617021</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="8">
+        <v>9.1915239999999994</v>
+      </c>
       <c r="AD103" s="8">
         <v>14.753</v>
       </c>
@@ -13635,7 +14416,9 @@
       <c r="AB104" s="8">
         <v>2.2976200000000002</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>6.9901619999999998</v>
+      </c>
       <c r="AD104" s="8">
         <v>15.015789473684212</v>
       </c>
@@ -13762,7 +14545,9 @@
       <c r="AB105" s="8">
         <v>9.6205128205128201</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>15.303438</v>
+      </c>
       <c r="AD105" s="8">
         <v>21.19125</v>
       </c>
@@ -13891,7 +14676,9 @@
       <c r="AB106" s="8">
         <v>1.4109375</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>7.6855520000000004</v>
+      </c>
       <c r="AD106" s="8">
         <v>14.6239578125</v>
       </c>
@@ -13942,7 +14729,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>44</v>
@@ -13978,25 +14765,61 @@
       <c t="s" r="N107" s="4">
         <v>52</v>
       </c>
-      <c r="O107" s="5"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="7"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-      <c r="X107" s="8"/>
-      <c r="Y107" s="6"/>
-      <c r="Z107" s="6"/>
-      <c r="AA107" s="8"/>
-      <c r="AB107" s="8"/>
-      <c r="AC107" s="8"/>
-      <c r="AD107" s="8"/>
-      <c r="AE107" s="6"/>
+      <c r="O107" s="5">
+        <v>5836.6499999999996</v>
+      </c>
+      <c r="P107" s="5">
+        <v>5836.6499999999996</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>-0.22988164509361519</v>
+      </c>
+      <c r="R107" s="7">
+        <v>69</v>
+      </c>
+      <c r="S107" s="6">
+        <v>-0.16867469879518071</v>
+      </c>
+      <c r="T107" s="6">
+        <v>0.56425396417465501</v>
+      </c>
+      <c r="U107" s="6">
+        <v>0.20215412950922193</v>
+      </c>
+      <c r="V107" s="6">
+        <v>0.03153298553108376</v>
+      </c>
+      <c r="W107" s="6">
+        <v>0.0074729510935211121</v>
+      </c>
+      <c r="X107" s="8">
+        <v>48.585947058823528</v>
+      </c>
+      <c r="Y107" s="6">
+        <v>0.68627450980392157</v>
+      </c>
+      <c r="Z107" s="6">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="AA107" s="8">
+        <v>15.506102816901407</v>
+      </c>
+      <c r="AB107" s="8">
+        <v>16.575666000000002</v>
+      </c>
+      <c r="AC107" s="8">
+        <v>32.489127000000003</v>
+      </c>
+      <c r="AD107" s="8">
+        <v>39.25424901960784</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>0.17647058823529413</v>
+      </c>
       <c r="AF107" s="9"/>
-      <c r="AG107" s="5"/>
+      <c r="AG107" s="5">
+        <v>0</v>
+      </c>
       <c r="AH107" s="10">
         <v>2</v>
       </c>
@@ -14206,7 +15029,9 @@
       <c r="AB109" s="8">
         <v>9.5253608695652172</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>13.399998999999999</v>
+      </c>
       <c r="AD109" s="8">
         <v>21.346378260869564</v>
       </c>
@@ -14428,7 +15253,9 @@
       <c r="AB111" s="8">
         <v>1.3525615384615386</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>7.8730760000000002</v>
+      </c>
       <c r="AD111" s="8">
         <v>14.844869230769232</v>
       </c>
@@ -14648,7 +15475,9 @@
       <c r="AB113" s="8">
         <v>6.660561386138613</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>11.979514999999999</v>
+      </c>
       <c r="AD113" s="8">
         <v>21.944554455445545</v>
       </c>
@@ -14777,7 +15606,9 @@
       <c r="AB114" s="8">
         <v>2.8963541666666668</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>4.8466769999999997</v>
+      </c>
       <c r="AD114" s="8">
         <v>12.512254901960784</v>
       </c>
@@ -14906,7 +15737,9 @@
       <c r="AB115" s="8">
         <v>3.9716140625</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>9.5422539999999998</v>
+      </c>
       <c r="AD115" s="8">
         <v>17.086519117647057</v>
       </c>
@@ -15128,7 +15961,9 @@
       <c r="AB117" s="8">
         <v>9.2771428571428576</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>14.439321</v>
+      </c>
       <c r="AD117" s="8">
         <v>17.464378431372548</v>
       </c>
@@ -15257,7 +16092,9 @@
       <c r="AB118" s="8">
         <v>18.082245652173913</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>30.957756</v>
+      </c>
       <c r="AD118" s="8">
         <v>36.898958333333333</v>
       </c>
@@ -15386,7 +16223,9 @@
       <c r="AB119" s="8">
         <v>4.3421568627450977</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>6.81928</v>
+      </c>
       <c r="AD119" s="8">
         <v>13.771241176470589</v>
       </c>
@@ -15513,7 +16352,9 @@
       <c r="AB120" s="8">
         <v>10.29215588235294</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>14.722156</v>
+      </c>
       <c r="AD120" s="8">
         <v>22.580391176470588</v>
       </c>
@@ -15640,7 +16481,9 @@
       <c r="AB121" s="8">
         <v>10.216669230769231</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>18.472548</v>
+      </c>
       <c r="AD121" s="8">
         <v>17.175491176470587</v>
       </c>
@@ -15652,7 +16495,7 @@
         <v>-161.80000000000001</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -15769,7 +16612,9 @@
       <c r="AB122" s="8">
         <v>3.5018931818181822</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>8.2044289999999993</v>
+      </c>
       <c r="AD122" s="8">
         <v>14.930434782608694</v>
       </c>
@@ -15898,7 +16743,9 @@
       <c r="AB123" s="8">
         <v>5.2563592105263153</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>7.7684800000000003</v>
+      </c>
       <c r="AD123" s="8">
         <v>15.728509210526317</v>
       </c>
@@ -16027,7 +16874,9 @@
       <c r="AB124" s="8">
         <v>11.172220000000001</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>17.198263000000001</v>
+      </c>
       <c r="AD124" s="8">
         <v>25.094446666666666</v>
       </c>
@@ -16156,7 +17005,9 @@
       <c r="AB125" s="8">
         <v>14.809701492537313</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>19.000039000000001</v>
+      </c>
       <c r="AD125" s="8">
         <v>26.816417910447761</v>
       </c>
@@ -16285,7 +17136,9 @@
       <c r="AB126" s="8">
         <v>13.060076744186047</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>16.896819000000001</v>
+      </c>
       <c r="AD126" s="8">
         <v>23.343561363636365</v>
       </c>
@@ -16414,7 +17267,9 @@
       <c r="AB127" s="8">
         <v>11.339103846153847</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>17.444656999999999</v>
+      </c>
       <c r="AD127" s="8">
         <v>27.317307692307693</v>
       </c>
@@ -16543,7 +17398,9 @@
       <c r="AB128" s="8">
         <v>16.730157142857145</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>26.609787000000001</v>
+      </c>
       <c r="AD128" s="8">
         <v>33.201585714285713</v>
       </c>
@@ -16672,7 +17529,9 @@
       <c r="AB129" s="8">
         <v>6.7689655172413801</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>13.567352</v>
+      </c>
       <c r="AD129" s="8">
         <v>19.877419354838711</v>
       </c>
@@ -16801,7 +17660,9 @@
       <c r="AB130" s="8">
         <v>19.288303508771929</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>26.318189</v>
+      </c>
       <c r="AD130" s="8">
         <v>33.209649122807015</v>
       </c>
@@ -16928,7 +17789,9 @@
       <c r="AB131" s="8">
         <v>8.3193000000000001</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>16.471928999999999</v>
+      </c>
       <c r="AD131" s="8">
         <v>23.426315789473687</v>
       </c>
@@ -17057,7 +17920,9 @@
       <c r="AB132" s="8">
         <v>4.0093335999999997</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>8.1834489999999995</v>
+      </c>
       <c r="AD132" s="8">
         <v>13.788461538461538</v>
       </c>
@@ -17108,7 +17973,7 @@
         <v>19775</v>
       </c>
       <c r="B133" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C133" s="4">
         <v>44</v>
@@ -17144,25 +18009,61 @@
       <c t="s" r="N133" s="4">
         <v>52</v>
       </c>
-      <c r="O133" s="5"/>
-      <c r="P133" s="5"/>
-      <c r="Q133" s="6"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="6"/>
-      <c r="T133" s="6"/>
-      <c r="U133" s="6"/>
-      <c r="V133" s="6"/>
-      <c r="W133" s="6"/>
-      <c r="X133" s="8"/>
-      <c r="Y133" s="6"/>
-      <c r="Z133" s="6"/>
-      <c r="AA133" s="8"/>
-      <c r="AB133" s="8"/>
-      <c r="AC133" s="8"/>
-      <c r="AD133" s="8"/>
-      <c r="AE133" s="6"/>
+      <c r="O133" s="5">
+        <v>7065.0200000000004</v>
+      </c>
+      <c r="P133" s="5">
+        <v>7065.0200000000004</v>
+      </c>
+      <c r="Q133" s="6">
+        <v>-0.041958440234105776</v>
+      </c>
+      <c r="R133" s="7">
+        <v>74</v>
+      </c>
+      <c r="S133" s="6">
+        <v>-0.12941176470588234</v>
+      </c>
+      <c r="T133" s="6">
+        <v>-0.00075725192568456981</v>
+      </c>
+      <c r="U133" s="6">
+        <v>-0.40178654837495154</v>
+      </c>
+      <c r="V133" s="6">
+        <v>0.025556827864606186</v>
+      </c>
+      <c r="W133" s="6">
+        <v>0.013709727644083101</v>
+      </c>
+      <c r="X133" s="8">
+        <v>57.046667499999998</v>
+      </c>
+      <c r="Y133" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="Z133" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="AA133" s="8">
+        <v>13.40529411764706</v>
+      </c>
+      <c r="AB133" s="8">
+        <v>15.927027027027027</v>
+      </c>
+      <c r="AC133" s="8">
+        <v>32.700985000000003</v>
+      </c>
+      <c r="AD133" s="8">
+        <v>38.266667499999997</v>
+      </c>
+      <c r="AE133" s="6">
+        <v>0.074999999999999997</v>
+      </c>
       <c r="AF133" s="9"/>
-      <c r="AG133" s="5"/>
+      <c r="AG133" s="5">
+        <v>0</v>
+      </c>
       <c r="AH133" s="10">
         <v>1</v>
       </c>
@@ -17281,7 +18182,9 @@
       <c r="AB134" s="8">
         <v>58.475286206896556</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>82.907578000000001</v>
+      </c>
       <c r="AD134" s="8">
         <v>87.713890000000006</v>
       </c>
@@ -17410,7 +18313,9 @@
       <c r="AB135" s="8">
         <v>3.4539205882352944</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>6.9754889999999996</v>
+      </c>
       <c r="AD135" s="8">
         <v>13.933332352941177</v>
       </c>
@@ -17461,7 +18366,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -17497,27 +18402,63 @@
       <c t="s" r="N136" s="4">
         <v>52</v>
       </c>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="8"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-      <c r="AA136" s="8"/>
-      <c r="AB136" s="8"/>
-      <c r="AC136" s="8"/>
-      <c r="AD136" s="8"/>
-      <c r="AE136" s="6"/>
+      <c r="O136" s="5">
+        <v>10018.73</v>
+      </c>
+      <c r="P136" s="5">
+        <v>10018.73</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>-0.15792574686829708</v>
+      </c>
+      <c r="R136" s="7">
+        <v>90</v>
+      </c>
+      <c r="S136" s="6">
+        <v>-0.20353982300884954</v>
+      </c>
+      <c r="T136" s="6">
+        <v>0.28405872800245147</v>
+      </c>
+      <c r="U136" s="6">
+        <v>0.0051311593385588794</v>
+      </c>
+      <c r="V136" s="6">
+        <v>0.0095286029267182566</v>
+      </c>
+      <c r="W136" s="6">
+        <v>-0.0010296215188951095</v>
+      </c>
+      <c r="X136" s="8">
+        <v>22.965277777777779</v>
+      </c>
+      <c r="Y136" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Z136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="8">
+        <v>4.4970366666666663</v>
+      </c>
+      <c r="AB136" s="8">
+        <v>5.130477142857143</v>
+      </c>
+      <c r="AC136" s="8">
+        <v>9.7244569999999992</v>
+      </c>
+      <c r="AD136" s="8">
+        <v>16.395369444444444</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>0.88888888888888884</v>
+      </c>
       <c r="AF136" s="9"/>
-      <c r="AG136" s="5"/>
+      <c r="AG136" s="5">
+        <v>-401.69999999999999</v>
+      </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -17556,7 +18497,7 @@
         <v>19787</v>
       </c>
       <c r="B137" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C137" s="4">
         <v>44</v>
@@ -17590,25 +18531,61 @@
       <c t="s" r="N137" s="4">
         <v>52</v>
       </c>
-      <c r="O137" s="5"/>
-      <c r="P137" s="5"/>
-      <c r="Q137" s="6"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="6"/>
-      <c r="T137" s="6"/>
-      <c r="U137" s="6"/>
-      <c r="V137" s="6"/>
-      <c r="W137" s="6"/>
-      <c r="X137" s="8"/>
-      <c r="Y137" s="6"/>
-      <c r="Z137" s="6"/>
-      <c r="AA137" s="8"/>
-      <c r="AB137" s="8"/>
-      <c r="AC137" s="8"/>
-      <c r="AD137" s="8"/>
-      <c r="AE137" s="6"/>
+      <c r="O137" s="5">
+        <v>6397.0200000000004</v>
+      </c>
+      <c r="P137" s="5">
+        <v>6397.0200000000004</v>
+      </c>
+      <c r="Q137" s="6">
+        <v>0.14940616296828679</v>
+      </c>
+      <c r="R137" s="7">
+        <v>71</v>
+      </c>
+      <c r="S137" s="6">
+        <v>0.14516129032258074</v>
+      </c>
+      <c r="T137" s="6">
+        <v>0.0089736002075966621</v>
+      </c>
+      <c r="U137" s="6">
+        <v>-0.30433947369243802</v>
+      </c>
+      <c r="V137" s="6">
+        <v>0.012880685068985244</v>
+      </c>
+      <c r="W137" s="6">
+        <v>-0.0064173630846863063</v>
+      </c>
+      <c r="X137" s="8">
+        <v>25.328260869565216</v>
+      </c>
+      <c r="Y137" s="6">
+        <v>0.47826086956521741</v>
+      </c>
+      <c r="Z137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="8">
+        <v>5.7734229729729725</v>
+      </c>
+      <c r="AB137" s="8">
+        <v>4.0608695652173914</v>
+      </c>
+      <c r="AC137" s="8">
+        <v>9.7557399999999994</v>
+      </c>
+      <c r="AD137" s="8">
+        <v>16.622465217391305</v>
+      </c>
+      <c r="AE137" s="6">
+        <v>0.91304347826086951</v>
+      </c>
       <c r="AF137" s="9"/>
-      <c r="AG137" s="5"/>
+      <c r="AG137" s="5">
+        <v>-892.17999999999995</v>
+      </c>
       <c r="AH137" s="10">
         <v>2</v>
       </c>
@@ -17725,7 +18702,9 @@
       <c r="AB138" s="8">
         <v>7.7491452991452991</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>12.771089</v>
+      </c>
       <c r="AD138" s="8">
         <v>19.363585714285716</v>
       </c>
@@ -17854,7 +18833,9 @@
       <c r="AB139" s="8">
         <v>1.7779338028169014</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>7.3172030000000001</v>
+      </c>
       <c r="AD139" s="8">
         <v>14.116667123287669</v>
       </c>
@@ -18171,7 +19152,9 @@
       <c r="AB142" s="8">
         <v>13.981410256410255</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>26.229534999999998</v>
+      </c>
       <c r="AD142" s="8">
         <v>34.663291139240506</v>
       </c>
@@ -18298,7 +19281,9 @@
       <c r="AB143" s="8">
         <v>7.0297097826086956</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>14.338575000000001</v>
+      </c>
       <c r="AD143" s="8">
         <v>22.291666304347824</v>
       </c>
@@ -18427,7 +19412,9 @@
       <c r="AB144" s="8">
         <v>3.6611113821138215</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>11.144076</v>
+      </c>
       <c r="AD144" s="8">
         <v>18.10298130081301</v>
       </c>
@@ -18556,7 +19543,9 @@
       <c r="AB145" s="8">
         <v>11.641146875</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>17.405674000000001</v>
+      </c>
       <c r="AD145" s="8">
         <v>22.050439473684211</v>
       </c>
@@ -18685,7 +19674,9 @@
       <c r="AB146" s="8">
         <v>7.2114203703703703</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>17.092327999999998</v>
+      </c>
       <c r="AD146" s="8">
         <v>22.759394545454544</v>
       </c>
@@ -18814,7 +19805,9 @@
       <c r="AB147" s="8">
         <v>2.0003036363636362</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>7.6484839999999998</v>
+      </c>
       <c r="AD147" s="8">
         <v>14.606059999999999</v>
       </c>
@@ -18867,7 +19860,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>44</v>
@@ -18903,25 +19896,61 @@
       <c t="s" r="N148" s="4">
         <v>52</v>
       </c>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="7"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-      <c r="V148" s="6"/>
-      <c r="W148" s="6"/>
-      <c r="X148" s="8"/>
-      <c r="Y148" s="6"/>
-      <c r="Z148" s="6"/>
-      <c r="AA148" s="8"/>
-      <c r="AB148" s="8"/>
-      <c r="AC148" s="8"/>
-      <c r="AD148" s="8"/>
-      <c r="AE148" s="6"/>
+      <c r="O148" s="5">
+        <v>8590.9400000000005</v>
+      </c>
+      <c r="P148" s="5">
+        <v>8590.9400000000005</v>
+      </c>
+      <c r="Q148" s="6">
+        <v>-0.24769890232101954</v>
+      </c>
+      <c r="R148" s="7">
+        <v>91</v>
+      </c>
+      <c r="S148" s="6">
+        <v>-0.31578947368421051</v>
+      </c>
+      <c r="T148" s="6">
+        <v>0.00097777425985980581</v>
+      </c>
+      <c r="U148" s="6">
+        <v>-0.30714915946334159</v>
+      </c>
+      <c r="V148" s="6">
+        <v>0.075376966897685221</v>
+      </c>
+      <c r="W148" s="6">
+        <v>0.050541500697246167</v>
+      </c>
+      <c r="X148" s="8">
+        <v>44.209859154929582</v>
+      </c>
+      <c r="Y148" s="6">
+        <v>0.49295774647887325</v>
+      </c>
+      <c r="Z148" s="6">
+        <v>0.52112676056338025</v>
+      </c>
+      <c r="AA148" s="8">
+        <v>10.023147777777778</v>
+      </c>
+      <c r="AB148" s="8">
+        <v>20.575245588235294</v>
+      </c>
+      <c r="AC148" s="8">
+        <v>30.926632999999999</v>
+      </c>
+      <c r="AD148" s="8">
+        <v>37.878404225352114</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>0.30985915492957744</v>
+      </c>
       <c r="AF148" s="9"/>
-      <c r="AG148" s="5"/>
+      <c r="AG148" s="5">
+        <v>0</v>
+      </c>
       <c r="AH148" s="10">
         <v>2</v>
       </c>
@@ -19040,7 +20069,9 @@
       <c r="AB149" s="8">
         <v>20.165909090909089</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>26.777272</v>
+      </c>
       <c r="AD149" s="8">
         <v>33.705304545454545</v>
       </c>
@@ -19167,7 +20198,9 @@
       <c r="AB150" s="8">
         <v>6.0053022727272722</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>11.974621000000001</v>
+      </c>
       <c r="AD150" s="8">
         <v>18.910227272727273</v>
       </c>
@@ -19395,7 +20428,9 @@
       <c r="AB152" s="8">
         <v>6.40490294117647</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>9.2058809999999998</v>
+      </c>
       <c r="AD152" s="8">
         <v>16.138235294117649</v>
       </c>
@@ -19524,7 +20559,9 @@
       <c r="AB153" s="8">
         <v>10.475613684210527</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>17.128738999999999</v>
+      </c>
       <c r="AD153" s="8">
         <v>24.849132291666667</v>
       </c>
@@ -19649,7 +20686,9 @@
       <c r="AB154" s="8">
         <v>9.6977486486486502</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>13.928943</v>
+      </c>
       <c r="AD154" s="8">
         <v>22.291879487179486</v>
       </c>
@@ -19661,7 +20700,7 @@
         <v>-5.5899999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -19776,7 +20815,9 @@
       <c r="AB155" s="8">
         <v>3.3766256097560978</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>5.549919</v>
+      </c>
       <c r="AD155" s="8">
         <v>11.59329268292683</v>
       </c>
@@ -19905,7 +20946,9 @@
       <c r="AB156" s="8">
         <v>5.1311111111111112</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>10.032961999999999</v>
+      </c>
       <c r="AD156" s="8">
         <v>16.964073333333332</v>
       </c>
@@ -20224,7 +21267,9 @@
       <c r="AB159" s="8">
         <v>6.1600000000000001</v>
       </c>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>11.71738</v>
+      </c>
       <c r="AD159" s="8">
         <v>18.638571428571428</v>
       </c>
@@ -20349,7 +21394,9 @@
       <c r="AB160" s="8">
         <v>9.8166674418604654</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>16.072092000000001</v>
+      </c>
       <c r="AD160" s="8">
         <v>23.013565116279072</v>
       </c>
@@ -20515,7 +21562,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20551,25 +21598,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>7585.5799999999999</v>
+      </c>
+      <c r="P162" s="5">
+        <v>7585.5799999999999</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.23926019824857692</v>
+      </c>
+      <c r="R162" s="7">
+        <v>86</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.21818181818181814</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.33406458042760079</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.010214960490826016</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.010439478589639816</v>
+      </c>
+      <c r="W162" s="6">
+        <v>-0.0018575375910609342</v>
+      </c>
+      <c r="X162" s="8">
+        <v>29.987082500000003</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>12.59083375</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>7.3198189189189193</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>19.943152000000001</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>26.890417500000002</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.47499999999999998</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-275.30000000000001</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20688,7 +21771,9 @@
       <c r="AB163" s="8">
         <v>7.9446731958762884</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>12.867725</v>
+      </c>
       <c r="AD163" s="8">
         <v>19.055763551401867</v>
       </c>
@@ -20817,7 +21902,9 @@
       <c r="AB164" s="8">
         <v>4.1098953125</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>9.4479229999999994</v>
+      </c>
       <c r="AD164" s="8">
         <v>15.536619718309858</v>
       </c>
@@ -21041,7 +22128,9 @@
       <c r="AB166" s="8">
         <v>16.973549999999999</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>22.971119000000002</v>
+      </c>
       <c r="AD166" s="8">
         <v>29.082291666666666</v>
       </c>
@@ -21170,7 +22259,9 @@
       <c r="AB167" s="8">
         <v>15.465032352941176</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>19.656378</v>
+      </c>
       <c r="AD167" s="8">
         <v>25.566185576923075</v>
       </c>
@@ -21299,7 +22390,9 @@
       <c r="AB168" s="8">
         <v>7.6932617021276597</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>12.497161999999999</v>
+      </c>
       <c r="AD168" s="8">
         <v>19.425176595744681</v>
       </c>
@@ -21428,7 +22521,9 @@
       <c r="AB169" s="8">
         <v>6.409802941176471</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>12.757488</v>
+      </c>
       <c r="AD169" s="8">
         <v>19.178702777777779</v>
       </c>
@@ -21557,7 +22652,9 @@
       <c r="AB170" s="8">
         <v>2.5833326923076925</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>7.0279870000000004</v>
+      </c>
       <c r="AD170" s="8">
         <v>13.876415094339624</v>
       </c>
@@ -21686,7 +22783,9 @@
       <c r="AB171" s="8">
         <v>4.040909090909091</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>8.4918610000000001</v>
+      </c>
       <c r="AD171" s="8">
         <v>15.065714285714284</v>
       </c>
@@ -21815,7 +22914,9 @@
       <c r="AB172" s="8">
         <v>4.8849999999999998</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>8.4653030000000005</v>
+      </c>
       <c r="AD172" s="8">
         <v>12.086363636363638</v>
       </c>
@@ -21944,7 +23045,9 @@
       <c r="AB173" s="8">
         <v>31.521213636363633</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>46.949316000000003</v>
+      </c>
       <c r="AD173" s="8">
         <v>33.188888235294115</v>
       </c>
@@ -22047,10 +23150,10 @@
         <v>-0.26717557251908397</v>
       </c>
       <c r="T174" s="6">
-        <v>0.28158175602243368</v>
+        <v>0.47503988560503208</v>
       </c>
       <c r="U174" s="6">
-        <v>-0.063007837111113921</v>
+        <v>0.13045029247148446</v>
       </c>
       <c r="V174" s="6">
         <v>0.034160233288614325</v>
@@ -22073,7 +23176,9 @@
       <c r="AB174" s="8">
         <v>4.8720837499999998</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>13.742499</v>
+      </c>
       <c r="AD174" s="8">
         <v>20.685624999999998</v>
       </c>
@@ -22124,7 +23229,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22160,25 +23265,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>7953.5299999999997</v>
+      </c>
+      <c r="P175" s="5">
+        <v>7953.5299999999997</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.20574528982651041</v>
+      </c>
+      <c r="R175" s="7">
+        <v>96</v>
+      </c>
+      <c r="S175" s="6">
+        <v>0.12941176470588234</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.44853776876430967</v>
+      </c>
+      <c r="U175" s="6">
+        <v>0.093925414250024833</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.026221375917359967</v>
+      </c>
+      <c r="W175" s="6">
+        <v>0.0054444378785268935</v>
+      </c>
+      <c r="X175" s="8">
+        <v>41.082352941176467</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.45098039215686275</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>14.066111111111111</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>5.9520408163265301</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>19.816419</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>26.107843137254903</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.21568627450980393</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-601.10000000000002</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22295,7 +23436,9 @@
       <c r="AB176" s="8">
         <v>8.0967741935483879</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>14.14086</v>
+      </c>
       <c r="AD176" s="8">
         <v>21.084409677419355</v>
       </c>
@@ -22424,7 +23567,9 @@
       <c r="AB177" s="8">
         <v>1.8179000000000001</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>5.3298050000000003</v>
+      </c>
       <c r="AD177" s="8">
         <v>12.368518518518519</v>
       </c>
@@ -22553,7 +23698,9 @@
       <c r="AB178" s="8">
         <v>3.2018749999999998</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>7.6535409999999997</v>
+      </c>
       <c r="AD178" s="8">
         <v>14.606041250000001</v>
       </c>
@@ -22680,7 +23827,9 @@
       <c r="AB179" s="8">
         <v>4.5373330000000003</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>27.819841</v>
+      </c>
       <c r="AD179" s="8">
         <v>34.714851485148515</v>
       </c>
@@ -22807,7 +23956,9 @@
       <c r="AB180" s="8">
         <v>16.498956249999999</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>19.805208</v>
+      </c>
       <c r="AD180" s="8">
         <v>27.761456249999998</v>
       </c>
@@ -22936,7 +24087,9 @@
       <c r="AB181" s="8">
         <v>2.3533333333333331</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>8.2469219999999996</v>
+      </c>
       <c r="AD181" s="8">
         <v>13.810456862745099</v>
       </c>
@@ -23065,7 +24218,9 @@
       <c r="AB182" s="8">
         <v>4.0517161764705882</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>9.5786650000000009</v>
+      </c>
       <c r="AD182" s="8">
         <v>15.606959340659342</v>
       </c>
@@ -23116,7 +24271,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
@@ -23152,25 +24307,61 @@
       <c t="s" r="N183" s="4">
         <v>52</v>
       </c>
-      <c r="O183" s="5"/>
-      <c r="P183" s="5"/>
-      <c r="Q183" s="6"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="6"/>
-      <c r="T183" s="6"/>
-      <c r="U183" s="6"/>
-      <c r="V183" s="6"/>
-      <c r="W183" s="6"/>
-      <c r="X183" s="8"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="6"/>
-      <c r="AA183" s="8"/>
-      <c r="AB183" s="8"/>
-      <c r="AC183" s="8"/>
-      <c r="AD183" s="8"/>
-      <c r="AE183" s="6"/>
+      <c r="O183" s="5">
+        <v>7506.04</v>
+      </c>
+      <c r="P183" s="5">
+        <v>7506.04</v>
+      </c>
+      <c r="Q183" s="6">
+        <v>0.2612564776416344</v>
+      </c>
+      <c r="R183" s="7">
+        <v>87</v>
+      </c>
+      <c r="S183" s="6">
+        <v>0.27941176470588225</v>
+      </c>
+      <c r="T183" s="6">
+        <v>3.1217759164619427</v>
+      </c>
+      <c r="U183" s="6">
+        <v>-1.6048509067364416</v>
+      </c>
+      <c r="V183" s="6">
+        <v>0.043581902041555869</v>
+      </c>
+      <c r="W183" s="6">
+        <v>0.016655586700843588</v>
+      </c>
+      <c r="X183" s="8">
+        <v>27.159226785714285</v>
+      </c>
+      <c r="Y183" s="6">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="Z183" s="6">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="AA183" s="8">
+        <v>7.8571709302325576</v>
+      </c>
+      <c r="AB183" s="8">
+        <v>5.4692307692307685</v>
+      </c>
+      <c r="AC183" s="8">
+        <v>11.964169999999999</v>
+      </c>
+      <c r="AD183" s="8">
+        <v>19.29791607142857</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>0.6964285714285714</v>
+      </c>
       <c r="AF183" s="9"/>
-      <c r="AG183" s="5"/>
+      <c r="AG183" s="5">
+        <v>-128.80000000000001</v>
+      </c>
       <c r="AH183" s="10">
         <v>4</v>
       </c>
@@ -23289,7 +24480,9 @@
       <c r="AB184" s="8">
         <v>8.616122826086956</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>17.60003</v>
+      </c>
       <c r="AD184" s="8">
         <v>25.639456122448983</v>
       </c>
@@ -23433,7 +24626,7 @@
         <v>19926</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>44</v>
@@ -23469,25 +24662,61 @@
       <c t="s" r="N186" s="4">
         <v>52</v>
       </c>
-      <c r="O186" s="5"/>
-      <c r="P186" s="5"/>
-      <c r="Q186" s="6"/>
-      <c r="R186" s="7"/>
-      <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
-      <c r="X186" s="8"/>
-      <c r="Y186" s="6"/>
-      <c r="Z186" s="6"/>
-      <c r="AA186" s="8"/>
-      <c r="AB186" s="8"/>
-      <c r="AC186" s="8"/>
-      <c r="AD186" s="8"/>
-      <c r="AE186" s="6"/>
+      <c r="O186" s="5">
+        <v>2790.9000000000001</v>
+      </c>
+      <c r="P186" s="5">
+        <v>2790.9000000000001</v>
+      </c>
+      <c r="Q186" s="6">
+        <v>-0.41826436048474847</v>
+      </c>
+      <c r="R186" s="7">
+        <v>30</v>
+      </c>
+      <c r="S186" s="6">
+        <v>-0.55223880597014929</v>
+      </c>
+      <c r="T186" s="6">
+        <v>0.39027120283779426</v>
+      </c>
+      <c r="U186" s="6">
+        <v>0.099035400766777734</v>
+      </c>
+      <c r="V186" s="6">
+        <v>0.10461625282167042</v>
+      </c>
+      <c r="W186" s="6">
+        <v>0.059713174961481957</v>
+      </c>
+      <c r="X186" s="8">
+        <v>37.725488235294115</v>
+      </c>
+      <c r="Y186" s="6">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="Z186" s="6">
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="AA186" s="8">
+        <v>15.814584375000001</v>
+      </c>
+      <c r="AB186" s="8">
+        <v>9.2480411764705881</v>
+      </c>
+      <c r="AC186" s="8">
+        <v>25.467483000000001</v>
+      </c>
+      <c r="AD186" s="8">
+        <v>32.026470588235298</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>0.17647058823529413</v>
+      </c>
       <c r="AF186" s="9"/>
-      <c r="AG186" s="5"/>
+      <c r="AG186" s="5">
+        <v>0</v>
+      </c>
       <c r="AH186" s="10">
         <v>2</v>
       </c>
@@ -23528,7 +24757,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23564,25 +24793,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>2316.8000000000002</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2316.8000000000002</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.15716868631381342</v>
+      </c>
+      <c r="R187" s="7">
+        <v>33</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.057142857142857162</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.38438363259668501</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.2883168594613259</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.23422500863259668</v>
+      </c>
+      <c r="X187" s="8">
+        <v>34.142307692307696</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>10.768094285714286</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>8.8019230769230763</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>18.514885</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>25.25</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.30769230769230771</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23703,7 +24968,9 @@
       <c r="AB188" s="8">
         <v>6.0655804347826088</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>10.638245</v>
+      </c>
       <c r="AD188" s="8">
         <v>16.872665999999999</v>
       </c>
@@ -23754,7 +25021,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23790,25 +25057,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>8238.4099999999999</v>
+      </c>
+      <c r="P189" s="5">
+        <v>8238.4099999999999</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.32833874015646458</v>
+      </c>
+      <c r="R189" s="7">
+        <v>113</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.17708333333333326</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.33796171834128186</v>
+      </c>
+      <c r="U189" s="6">
+        <v>-0.010265670196069387</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.053417589073619792</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.031856389764529813</v>
+      </c>
+      <c r="X189" s="8">
+        <v>28.92450980392157</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.13725490196078433</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>7.7990110169491533</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>10.568229166666667</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>18.562514</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>24.784640196078431</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.59803921568627449</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23849,7 +25152,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -23885,25 +25188,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>9142.7399999999998</v>
+      </c>
+      <c r="P190" s="5">
+        <v>9142.7399999999998</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.15650688154226255</v>
+      </c>
+      <c r="R190" s="7">
+        <v>102</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.19047619047619047</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.24447901832492228</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.25523113421140708</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.045911346051621282</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.030805371256319224</v>
+      </c>
+      <c r="X190" s="8">
+        <v>31.383333333333333</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>6.79309797979798</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>8.305128205128204</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>15.659492999999999</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>21.701190476190476</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-172.40000000000001</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24018,7 +25357,9 @@
       <c r="AB191" s="8">
         <v>11.452652272727272</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>22.318937999999999</v>
+      </c>
       <c r="AD191" s="8">
         <v>29.270074999999999</v>
       </c>
@@ -24069,7 +25410,7 @@
         <v>19936</v>
       </c>
       <c r="B192" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C192" s="4">
         <v>44</v>
@@ -24105,25 +25446,59 @@
       <c t="s" r="N192" s="4">
         <v>52</v>
       </c>
-      <c r="O192" s="5"/>
-      <c r="P192" s="5"/>
+      <c r="O192" s="5">
+        <v>3889.4499999999998</v>
+      </c>
+      <c r="P192" s="5">
+        <v>3889.4499999999998</v>
+      </c>
       <c r="Q192" s="6"/>
-      <c r="R192" s="7"/>
-      <c r="S192" s="6"/>
-      <c r="T192" s="6"/>
-      <c r="U192" s="6"/>
-      <c r="V192" s="6"/>
-      <c r="W192" s="6"/>
-      <c r="X192" s="8"/>
-      <c r="Y192" s="6"/>
-      <c r="Z192" s="6"/>
-      <c r="AA192" s="8"/>
-      <c r="AB192" s="8"/>
-      <c r="AC192" s="8"/>
-      <c r="AD192" s="8"/>
-      <c r="AE192" s="6"/>
+      <c r="R192" s="7">
+        <v>41</v>
+      </c>
+      <c r="S192" s="6">
+        <v>-0.37878787878787878</v>
+      </c>
+      <c r="T192" s="6">
+        <v>0.27315317075679085</v>
+      </c>
+      <c r="U192" s="6">
+        <v>-0.043485428531026236</v>
+      </c>
+      <c r="V192" s="6">
+        <v>0.052986411960559976</v>
+      </c>
+      <c r="W192" s="6">
+        <v>0.023547802388512513</v>
+      </c>
+      <c r="X192" s="8">
+        <v>41.016668000000003</v>
+      </c>
+      <c r="Y192" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="Z192" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="AA192" s="8">
+        <v>4.4930902439024392</v>
+      </c>
+      <c r="AB192" s="8">
+        <v>23.026</v>
+      </c>
+      <c r="AC192" s="8">
+        <v>27.595870999999999</v>
+      </c>
+      <c r="AD192" s="8">
+        <v>34.464668000000003</v>
+      </c>
+      <c r="AE192" s="6">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="AF192" s="9"/>
-      <c r="AG192" s="5"/>
+      <c r="AG192" s="5">
+        <v>0</v>
+      </c>
       <c r="AH192" s="10">
         <v>2</v>
       </c>
@@ -24240,7 +25615,9 @@
       <c r="AB193" s="8">
         <v>7.0079999999999991</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>12.524134</v>
+      </c>
       <c r="AD193" s="8">
         <v>15.325116901408451</v>
       </c>
@@ -24293,7 +25670,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>44</v>
@@ -24329,25 +25706,61 @@
       <c t="s" r="N194" s="4">
         <v>52</v>
       </c>
-      <c r="O194" s="5"/>
-      <c r="P194" s="5"/>
-      <c r="Q194" s="6"/>
-      <c r="R194" s="7"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
-      <c r="X194" s="8"/>
-      <c r="Y194" s="6"/>
-      <c r="Z194" s="6"/>
-      <c r="AA194" s="8"/>
-      <c r="AB194" s="8"/>
-      <c r="AC194" s="8"/>
-      <c r="AD194" s="8"/>
-      <c r="AE194" s="6"/>
+      <c r="O194" s="5">
+        <v>3645</v>
+      </c>
+      <c r="P194" s="5">
+        <v>3645</v>
+      </c>
+      <c r="Q194" s="6">
+        <v>-0.22098739046804872</v>
+      </c>
+      <c r="R194" s="7">
+        <v>45</v>
+      </c>
+      <c r="S194" s="6">
+        <v>-0.23728813559322037</v>
+      </c>
+      <c r="T194" s="6">
+        <v>0.47951684499314129</v>
+      </c>
+      <c r="U194" s="6">
+        <v>0.08591465020576132</v>
+      </c>
+      <c r="V194" s="6">
+        <v>0.13413731138545953</v>
+      </c>
+      <c r="W194" s="6">
+        <v>0.081229218106995876</v>
+      </c>
+      <c r="X194" s="8">
+        <v>43.718940909090911</v>
+      </c>
+      <c r="Y194" s="6">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z194" s="6">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="AA194" s="8">
+        <v>11.052897826086957</v>
+      </c>
+      <c r="AB194" s="8">
+        <v>11.055557142857143</v>
+      </c>
+      <c r="AC194" s="8">
+        <v>22.051009000000001</v>
+      </c>
+      <c r="AD194" s="8">
+        <v>28.507142857142856</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>0.40909090909090912</v>
+      </c>
       <c r="AF194" s="9"/>
-      <c r="AG194" s="5"/>
+      <c r="AG194" s="5">
+        <v>-36.899999999999999</v>
+      </c>
       <c r="AH194" s="10">
         <v>2</v>
       </c>
@@ -24561,7 +25974,9 @@
       <c r="AB196" s="8">
         <v>14.739395454545456</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>30.581368000000001</v>
+      </c>
       <c r="AD196" s="8">
         <v>34.147434615384618</v>
       </c>
@@ -24690,7 +26105,9 @@
       <c r="AB197" s="8">
         <v>5.2580734375000002</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>7.5903790000000004</v>
+      </c>
       <c r="AD197" s="8">
         <v>14.420256923076922</v>
       </c>
@@ -24819,7 +26236,9 @@
       <c r="AB198" s="8">
         <v>5.4290111111111115</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>16.854873999999999</v>
+      </c>
       <c r="AD198" s="8">
         <v>23.07643793103448</v>
       </c>
@@ -24870,7 +26289,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -24906,25 +26325,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>9136.9300000000003</v>
+      </c>
+      <c r="P199" s="5">
+        <v>9136.9300000000003</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.17784788314678723</v>
+      </c>
+      <c r="R199" s="7">
+        <v>98</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.27407407407407403</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.3248937553423305</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.03226012457138229</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.014891106750297966</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-5.3737962313380969E-05</v>
+      </c>
+      <c r="X199" s="8">
+        <v>53.557922950819673</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.18032786885245902</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0.65573770491803274</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>17.03230206185567</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>13.074044262295082</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>34.307921999999998</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>41.224590163934423</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.18032786885245902</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-229.44999999999999</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -24965,7 +26420,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25001,25 +26456,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>3025.0999999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>3025.0999999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.083476896738215345</v>
+      </c>
+      <c r="R200" s="7">
+        <v>40</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.42657763379722985</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.11073551287560741</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.071480612211166569</v>
+      </c>
+      <c r="X200" s="8">
+        <v>35.621665</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>9.8567452380952378</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>6.8166650000000004</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>17.460605000000001</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>24.016665</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-80.900000000000006</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25231,7 +26722,9 @@
       <c r="AB202" s="8">
         <v>14.09752962962963</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>19.764790999999999</v>
+      </c>
       <c r="AD202" s="8">
         <v>26.037499999999998</v>
       </c>
@@ -25453,7 +26946,9 @@
       <c r="AB204" s="8">
         <v>8.2504638888888895</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>23.654409000000001</v>
+      </c>
       <c r="AD204" s="8">
         <v>30.366667567567571</v>
       </c>
@@ -25578,7 +27073,9 @@
       <c r="AB205" s="8">
         <v>4.6402791666666667</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>10.900277000000001</v>
+      </c>
       <c r="AD205" s="8">
         <v>17.978470833333333</v>
       </c>
@@ -25629,7 +27126,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25665,25 +27162,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>3265.5999999999999</v>
+      </c>
+      <c r="P206" s="5">
+        <v>3265.5999999999999</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>36</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.37157502449779523</v>
+      </c>
+      <c r="U206" s="6">
+        <v>-0.01636593581577658</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.026342785399314065</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.01174516168544831</v>
+      </c>
+      <c r="X206" s="8">
+        <v>31.32563846153846</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>5.5828694444444444</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>7.8602538461538467</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>14.507875</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>20.265384615384615</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-170.30000000000001</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -25724,7 +27253,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -25760,25 +27289,49 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>0</v>
+      </c>
+      <c r="P207" s="5">
+        <v>0</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>48</v>
+      </c>
       <c r="S207" s="6"/>
       <c r="T207" s="6"/>
       <c r="U207" s="6"/>
       <c r="V207" s="6"/>
       <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="X207" s="8">
+        <v>39.870173684210528</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>11.812319565217392</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>15.511405263157895</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>26.290569000000001</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>33.578068421052627</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.36842105263157893</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>0</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>
@@ -25893,7 +27446,9 @@
       <c r="AB208" s="8">
         <v>4.7722222222222221</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>19.020047999999999</v>
+      </c>
       <c r="AD208" s="8">
         <v>26.58941746031746</v>
       </c>
@@ -26202,7 +27757,9 @@
       <c r="AB211" s="8">
         <v>13.784000000000001</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>19.842666000000001</v>
+      </c>
       <c r="AD211" s="8">
         <v>26.751999999999999</v>
       </c>
@@ -26677,22 +28234,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -26702,10 +28261,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-27).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-27).xlsx
@@ -912,30 +912,30 @@
   </si>
   <si>
     <t>214
-167</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.672.950,79</t>
-  </si>
-  <si>
-    <t>R$ 9.451,70
-R$ 9.628,16</t>
-  </si>
-  <si>
-    <t>(3.4%)
-(1.9%)</t>
-  </si>
-  <si>
-    <t>102.8</t>
-  </si>
-  <si>
-    <t>(7.0%)</t>
-  </si>
-  <si>
-    <t>33.3%</t>
+172</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.708.333,54</t>
+  </si>
+  <si>
+    <t>R$ 9.386,45
+R$ 9.553,99</t>
+  </si>
+  <si>
+    <t>(3.2%)
+(1.7%)</t>
+  </si>
+  <si>
+    <t>102.2</t>
+  </si>
+  <si>
+    <t>(6.7%)</t>
+  </si>
+  <si>
+    <t>33.1%</t>
   </si>
   <si>
     <t>(10.3%)</t>
@@ -944,34 +944,34 @@
     <t>2.6%</t>
   </si>
   <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>30.7</t>
-  </si>
-  <si>
-    <t>59.7%</t>
-  </si>
-  <si>
-    <t>17.5%</t>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>30.9</t>
+  </si>
+  <si>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>17.6%</t>
   </si>
   <si>
     <t>7.6</t>
   </si>
   <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>15.7</t>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>15.8</t>
   </si>
   <si>
     <t>22.4</t>
   </si>
   <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>-R$ 43.869,46</t>
+    <t>59.9%</t>
+  </si>
+  <si>
+    <t>-R$ 44.195,96</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>10.281496062992126</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>18.382407000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>25.27178503937008</v>
       </c>
@@ -5813,10 +5815,10 @@
         <v>1.4285714285714284</v>
       </c>
       <c r="T35" s="6">
-        <v>7.1157854247358223</v>
+        <v>7.0704816261572239</v>
       </c>
       <c r="U35" s="6">
-        <v>4.6032372640268262</v>
+        <v>4.5579334654482269</v>
       </c>
       <c r="V35" s="6">
         <v>0.059445219139965089</v>
@@ -5894,7 +5896,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5930,25 +5932,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>6850.7200000000003</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6850.7200000000003</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.041103636704654556</v>
+      </c>
+      <c r="R36" s="7">
+        <v>89</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.27142857142857135</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.36177992970081974</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.030822015788121538</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.069973375061307422</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.036201742298619707</v>
+      </c>
+      <c r="X36" s="8">
+        <v>37.236075949367091</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.77215189873417722</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.36708860759493672</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.7196965909090913</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>11.923246052631578</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>23.021518987341771</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.39240506329113922</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6644,7 +6680,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6680,25 +6716,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>7347.4399999999996</v>
+      </c>
+      <c r="P42" s="5">
+        <v>7347.4399999999996</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.26312387396680004</v>
+      </c>
+      <c r="R42" s="7">
+        <v>80</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.26984126984126977</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.34499323573925073</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.026010025260498896</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.033672272247204468</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.008871797524035583</v>
+      </c>
+      <c r="X42" s="8">
+        <v>28.523333333333333</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.0517089743589745</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>9.3375711864406785</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>15.803402999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>22.573611666666668</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7779,7 +7851,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7815,25 +7887,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1213.48</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1213.48</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.44616760837220337</v>
+      </c>
+      <c r="R51" s="7">
+        <v>11</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.54166666666666674</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.28620990869235585</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.016439084286514815</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.089050911428288887</v>
+      </c>
+      <c r="X51" s="8">
+        <v>10.8104125</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>1.8500000000000001</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>1.0805499999999999</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>8.7145875000000004</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8706,7 +8812,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>19.551832999999998</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -10936,7 +11044,9 @@
       <c r="AB76" s="8">
         <v>9.3955031746031743</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>12.366758000000001</v>
+      </c>
       <c r="AD76" s="8">
         <v>20.515422388059701</v>
       </c>
@@ -14112,7 +14222,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14148,25 +14258,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>8059.6300000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>8059.6300000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.15486671137323671</v>
+      </c>
+      <c r="R102" s="7">
+        <v>87</v>
+      </c>
+      <c r="S102" s="6">
+        <v>0.060975609756097615</v>
+      </c>
+      <c r="T102" s="6">
+        <v>1.394604963255137E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.32411507724299998</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.02323375886982405</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.0098088249708733512</v>
+      </c>
+      <c r="X102" s="8">
+        <v>70.784426229508199</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.42622950819672129</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>9.7945079545454536</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>41.501307843137255</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>38.990303636363635</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.4098360655737705</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -25801,7 +25945,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25837,25 +25981,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>11911.48</v>
+      </c>
+      <c r="P195" s="5">
+        <v>11911.48</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.037532946941704948</v>
+      </c>
+      <c r="R195" s="7">
+        <v>131</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.029629629629629672</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.29648415646082604</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.024630432154526559</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.016108871441668039</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0026907235708744843</v>
+      </c>
+      <c r="X195" s="8">
+        <v>27.822826086956521</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.5380574803149605</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>8.096519780219781</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>19.452355434782611</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.70652173913043481</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-326.5</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
